--- a/01_stpa_steps_1_to_4/Step1_LGPD_provisions_per_hazard.xlsx
+++ b/01_stpa_steps_1_to_4/Step1_LGPD_provisions_per_hazard.xlsx
@@ -705,7 +705,7 @@
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Note: Art. 42 (civil liability) is not consolidated in H-6 because the mapping of Step 9 is delimited to the provisions with direct implications for system design (Chapter 7, Section 7.2). The provisions of H-4 and H-5 were consolidated during the writing of Chapter 5 from the themes of the hazards and are recorded here as the instrument of record.</t>
+          <t>Note: Art. 42 (civil liability) is not consolidated in H-6 because the mapping of Step 9 is delimited to the provisions with direct implications for system design (Chapter 7, Section 7.2). The provisions of H-4 and H-5 were consolidated during the writing of Chapter 5 from the themes of the hazards and are recorded here.</t>
         </is>
       </c>
     </row>
